--- a/artfynd/A 56912-2019 artfynd.xlsx
+++ b/artfynd/A 56912-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121151204</v>
+        <v>121151206</v>
       </c>
       <c r="B2" t="n">
-        <v>91975</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632781</v>
+        <v>632740</v>
       </c>
       <c r="R2" t="n">
-        <v>7198251</v>
+        <v>7198159</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151209</v>
+        <v>121151207</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>79717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632701</v>
+        <v>632718</v>
       </c>
       <c r="R3" t="n">
-        <v>7198294</v>
+        <v>7198236</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121151205</v>
       </c>
       <c r="B4" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151208</v>
+        <v>121151204</v>
       </c>
       <c r="B5" t="n">
-        <v>79216</v>
+        <v>91985</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632708</v>
+        <v>632781</v>
       </c>
       <c r="R5" t="n">
-        <v>7198247</v>
+        <v>7198251</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121151206</v>
+        <v>121151209</v>
       </c>
       <c r="B6" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632740</v>
+        <v>632701</v>
       </c>
       <c r="R6" t="n">
-        <v>7198159</v>
+        <v>7198294</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121151207</v>
+        <v>121151208</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>79219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632718</v>
+        <v>632708</v>
       </c>
       <c r="R7" t="n">
-        <v>7198236</v>
+        <v>7198247</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 56912-2019 artfynd.xlsx
+++ b/artfynd/A 56912-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121151206</v>
+        <v>121151207</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632740</v>
+        <v>632718</v>
       </c>
       <c r="R2" t="n">
-        <v>7198159</v>
+        <v>7198236</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151207</v>
+        <v>121151205</v>
       </c>
       <c r="B3" t="n">
-        <v>79717</v>
+        <v>91259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632718</v>
+        <v>632747</v>
       </c>
       <c r="R3" t="n">
-        <v>7198236</v>
+        <v>7198143</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121151205</v>
+        <v>121151206</v>
       </c>
       <c r="B4" t="n">
-        <v>91259</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632747</v>
+        <v>632740</v>
       </c>
       <c r="R4" t="n">
-        <v>7198143</v>
+        <v>7198159</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121151209</v>
+        <v>121151208</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632701</v>
+        <v>632708</v>
       </c>
       <c r="R6" t="n">
-        <v>7198294</v>
+        <v>7198247</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121151208</v>
+        <v>121151209</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632708</v>
+        <v>632701</v>
       </c>
       <c r="R7" t="n">
-        <v>7198247</v>
+        <v>7198294</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 56912-2019 artfynd.xlsx
+++ b/artfynd/A 56912-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121151207</v>
+        <v>121151204</v>
       </c>
       <c r="B2" t="n">
-        <v>79717</v>
+        <v>91997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632718</v>
+        <v>632781</v>
       </c>
       <c r="R2" t="n">
-        <v>7198236</v>
+        <v>7198251</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151205</v>
+        <v>121151207</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
+        <v>79720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632747</v>
+        <v>632718</v>
       </c>
       <c r="R3" t="n">
-        <v>7198143</v>
+        <v>7198236</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121151206</v>
+        <v>121151205</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>91271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632740</v>
+        <v>632747</v>
       </c>
       <c r="R4" t="n">
-        <v>7198159</v>
+        <v>7198143</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151204</v>
+        <v>121151209</v>
       </c>
       <c r="B5" t="n">
-        <v>91985</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632781</v>
+        <v>632701</v>
       </c>
       <c r="R5" t="n">
-        <v>7198251</v>
+        <v>7198294</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121151208</v>
+        <v>121151206</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632708</v>
+        <v>632740</v>
       </c>
       <c r="R6" t="n">
-        <v>7198247</v>
+        <v>7198159</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121151209</v>
+        <v>121151208</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>79222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632701</v>
+        <v>632708</v>
       </c>
       <c r="R7" t="n">
-        <v>7198294</v>
+        <v>7198247</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 56912-2019 artfynd.xlsx
+++ b/artfynd/A 56912-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121151204</v>
       </c>
       <c r="B2" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151207</v>
+        <v>121151209</v>
       </c>
       <c r="B3" t="n">
-        <v>79720</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632718</v>
+        <v>632701</v>
       </c>
       <c r="R3" t="n">
-        <v>7198236</v>
+        <v>7198294</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121151205</v>
       </c>
       <c r="B4" t="n">
-        <v>91271</v>
+        <v>91272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151209</v>
+        <v>121151206</v>
       </c>
       <c r="B5" t="n">
         <v>79685</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632701</v>
+        <v>632740</v>
       </c>
       <c r="R5" t="n">
-        <v>7198294</v>
+        <v>7198159</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121151206</v>
+        <v>121151208</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>79222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632740</v>
+        <v>632708</v>
       </c>
       <c r="R6" t="n">
-        <v>7198159</v>
+        <v>7198247</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121151208</v>
+        <v>121151207</v>
       </c>
       <c r="B7" t="n">
-        <v>79222</v>
+        <v>79720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632708</v>
+        <v>632718</v>
       </c>
       <c r="R7" t="n">
-        <v>7198247</v>
+        <v>7198236</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 56912-2019 artfynd.xlsx
+++ b/artfynd/A 56912-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121151204</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151209</v>
+        <v>121151208</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632701</v>
+        <v>632708</v>
       </c>
       <c r="R3" t="n">
-        <v>7198294</v>
+        <v>7198247</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121151205</v>
       </c>
       <c r="B4" t="n">
-        <v>91272</v>
+        <v>91275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151206</v>
+        <v>121151207</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>79723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632740</v>
+        <v>632718</v>
       </c>
       <c r="R5" t="n">
-        <v>7198159</v>
+        <v>7198236</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121151208</v>
+        <v>121151209</v>
       </c>
       <c r="B6" t="n">
-        <v>79222</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632708</v>
+        <v>632701</v>
       </c>
       <c r="R6" t="n">
-        <v>7198247</v>
+        <v>7198294</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121151207</v>
+        <v>121151206</v>
       </c>
       <c r="B7" t="n">
-        <v>79720</v>
+        <v>79688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632718</v>
+        <v>632740</v>
       </c>
       <c r="R7" t="n">
-        <v>7198236</v>
+        <v>7198159</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 56912-2019 artfynd.xlsx
+++ b/artfynd/A 56912-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121151204</v>
+        <v>121151206</v>
       </c>
       <c r="B2" t="n">
-        <v>92001</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632781</v>
+        <v>632740</v>
       </c>
       <c r="R2" t="n">
-        <v>7198251</v>
+        <v>7198159</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151208</v>
+        <v>121151205</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>91275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632708</v>
+        <v>632747</v>
       </c>
       <c r="R3" t="n">
-        <v>7198247</v>
+        <v>7198143</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121151205</v>
+        <v>121151208</v>
       </c>
       <c r="B4" t="n">
-        <v>91275</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632747</v>
+        <v>632708</v>
       </c>
       <c r="R4" t="n">
-        <v>7198143</v>
+        <v>7198247</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121151207</v>
+        <v>121151209</v>
       </c>
       <c r="B5" t="n">
-        <v>79723</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632718</v>
+        <v>632701</v>
       </c>
       <c r="R5" t="n">
-        <v>7198236</v>
+        <v>7198294</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121151209</v>
+        <v>121151204</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>92001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632701</v>
+        <v>632781</v>
       </c>
       <c r="R6" t="n">
-        <v>7198294</v>
+        <v>7198251</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121151206</v>
+        <v>121151207</v>
       </c>
       <c r="B7" t="n">
-        <v>79688</v>
+        <v>79723</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632740</v>
+        <v>632718</v>
       </c>
       <c r="R7" t="n">
-        <v>7198159</v>
+        <v>7198236</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
